--- a/projects/offline_asr_llm_aiot_uart_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/projects/offline_asr_llm_aiot_uart_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -645,7 +645,7 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>小沐小沐</t>
+          <t>你好灵犀</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -695,7 +695,7 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hello小沐</t>
+          <t>灵犀你好</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>嗨小沐</t>
+          <t>小沐小沐</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hello摸摸</t>
+          <t>hello小沐</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -845,7 +845,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hi摸摸</t>
+          <t>嗨小沐</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -857,7 +857,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hello慕慕</t>
+          <t>hello摸摸</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -945,7 +945,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hi慕慕</t>
+          <t>hi摸摸</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -995,7 +995,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI模式</t>
+          <t>hello慕慕</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -1007,11 +1007,11 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1045,15 +1045,15 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>聊天模式</t>
+          <t>hi慕慕</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0x000A</t>
+          <t>0x000B</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1088,22 +1088,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>翻译模式</t>
+          <t>AI模式</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0x000B</t>
+          <t>0x000C</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -1138,26 +1138,26 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>多语言模式</t>
+          <t>聊天模式</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0x000B</t>
+          <t>0x000C</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -1188,22 +1188,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>蓝牙模式</t>
+          <t>翻译模式</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000D</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1238,14 +1238,14 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>放首歌</t>
+          <t>多语言模式</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -1257,7 +1257,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1295,19 +1295,19 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>来首歌</t>
+          <t>蓝牙模式</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000E</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -1338,26 +1338,26 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>播放音乐</t>
+          <t>放首歌</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1388,26 +1388,26 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>打开音乐</t>
+          <t>来首歌</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1438,22 +1438,22 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>来点音乐</t>
+          <t>播放音乐</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -1488,22 +1488,22 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>来首音乐</t>
+          <t>打开音乐</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -1538,22 +1538,22 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>我要听歌</t>
+          <t>来点音乐</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1588,22 +1588,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>我想听歌</t>
+          <t>来首音乐</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1638,22 +1638,22 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>关闭音乐</t>
+          <t>我要听歌</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0x000E</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -1688,22 +1688,22 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>退出音乐</t>
+          <t>我想听歌</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0x000E</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -1738,26 +1738,26 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>静音</t>
+          <t>关闭音乐</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -1780,34 +1780,34 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>16</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>闭嘴</t>
+          <t>退出音乐</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -1838,26 +1838,26 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>关音效</t>
+          <t>静音</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1888,26 +1888,26 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>关声音</t>
+          <t>闭嘴</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1938,26 +1938,26 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>打开静音</t>
+          <t>关音效</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -1988,26 +1988,26 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="n"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>不要说话</t>
+          <t>关声音</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2038,22 +2038,22 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="2" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>关闭音效</t>
+          <t>打开静音</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="2" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>关闭声音</t>
+          <t>不要说话</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -2138,22 +2138,22 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="2" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>声音关闭</t>
+          <t>关闭音效</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2188,26 +2188,26 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="2" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>把音效关了</t>
+          <t>关闭声音</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -2238,26 +2238,26 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="2" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>把声音关了</t>
+          <t>声音关闭</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -2288,26 +2288,26 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>开声音</t>
+          <t>把音效关了</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2338,26 +2338,26 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="2" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>取消静音</t>
+          <t>把声音关了</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2388,26 +2388,26 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="2" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>关闭静音</t>
+          <t>开声音</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2438,22 +2438,22 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="2" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>打开声音</t>
+          <t>取消静音</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -2488,22 +2488,22 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="2" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>开启音量</t>
+          <t>关闭静音</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -2538,22 +2538,22 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="2" t="n"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>音效打开</t>
+          <t>打开声音</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -2588,22 +2588,22 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="2" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>声音打开</t>
+          <t>开启音量</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -2638,22 +2638,22 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="2" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>恢复声音</t>
+          <t>音效打开</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -2688,26 +2688,26 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="2" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>可以说话了</t>
+          <t>声音打开</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -2738,26 +2738,26 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="2" t="n"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>恢复声音</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -2788,14 +2788,14 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="2" t="n"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>播放</t>
+          <t>可以说话了</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -2807,7 +2807,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2830,7 +2830,7 @@
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -2845,19 +2845,19 @@
       <c r="B48" s="2" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>请播放</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -2888,26 +2888,26 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="2" t="n"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>继续播放</t>
+          <t>播放</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2938,26 +2938,26 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="2" t="n"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>取消暂停</t>
+          <t>请播放</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -2988,26 +2988,26 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="2" t="n"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>上一首</t>
+          <t>继续播放</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0x0013</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3038,26 +3038,26 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="2" t="n"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>上一曲</t>
+          <t>取消暂停</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0x0013</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3088,26 +3088,26 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="2" t="n"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>切歌</t>
+          <t>上一首</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0015</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3138,22 +3138,22 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="2" t="n"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>下一首</t>
+          <t>上一曲</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0015</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -3188,26 +3188,26 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="2" t="n"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>下一曲</t>
+          <t>切歌</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3238,22 +3238,22 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="2" t="n"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>换一首</t>
+          <t>下一首</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -3288,22 +3288,22 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="2" t="n"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>换一曲</t>
+          <t>下一曲</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
@@ -3338,26 +3338,26 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="2" t="n"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>音量最大</t>
+          <t>换一首</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -3388,26 +3388,26 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="2" t="n"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>声音最大</t>
+          <t>换一曲</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -3438,26 +3438,26 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="2" t="n"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>音量调到最大</t>
+          <t>音量最大</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3488,22 +3488,22 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="2" t="n"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>音量最小</t>
+          <t>声音最大</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -3538,26 +3538,26 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="2" t="n"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>声音最小</t>
+          <t>音量调到最大</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3588,26 +3588,26 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="2" t="n"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>音量调到最小</t>
+          <t>音量最小</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -3638,26 +3638,26 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="2" t="n"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>听不清</t>
+          <t>声音最小</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -3688,26 +3688,26 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="2" t="n"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>大声一点</t>
+          <t>音量调到最小</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -3738,26 +3738,26 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="2" t="n"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>音量调大</t>
+          <t>听不清</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         </is>
       </c>
       <c r="K66" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3788,26 +3788,26 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="2" t="n"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>声音大一点</t>
+          <t>大声一点</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -3838,26 +3838,26 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="2" t="n"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>声音太小了</t>
+          <t>音量调大</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3888,26 +3888,26 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="2" t="n"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>把声音加大一点</t>
+          <t>声音大一点</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -3938,26 +3938,26 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="2" t="n"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>把音量加大一点</t>
+          <t>声音太小了</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -3988,26 +3988,26 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="2" t="n"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>小声一点</t>
+          <t>把声音加大一点</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4038,26 +4038,26 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="2" t="n"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>音量调小</t>
+          <t>把音量加大一点</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4088,26 +4088,26 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="2" t="n"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>声音小一点</t>
+          <t>小声一点</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4138,26 +4138,26 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="2" t="n"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>声音太大了</t>
+          <t>音量调小</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4188,26 +4188,26 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="2" t="n"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>把声音减小一点</t>
+          <t>声音小一点</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4238,26 +4238,26 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="2" t="n"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>把音量减小一点</t>
+          <t>声音太大了</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4288,26 +4288,26 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="2" t="n"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>设置闹钟</t>
+          <t>把声音减小一点</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4338,26 +4338,26 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="2" t="n"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>设定闹钟</t>
+          <t>把音量减小一点</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4388,22 +4388,22 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="2" t="n"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>打开闹钟</t>
+          <t>设置闹钟</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
@@ -4438,22 +4438,22 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="2" t="n"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>关闭闹钟</t>
+          <t>设定闹钟</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
@@ -4488,22 +4488,22 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="n"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>取消闹钟</t>
+          <t>打开闹钟</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -4538,22 +4538,22 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="2" t="n"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>停止闹钟</t>
+          <t>关闭闹钟</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -4588,26 +4588,26 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="2" t="n"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>开灯</t>
+          <t>取消闹钟</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -4630,7 +4630,7 @@
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -4638,26 +4638,26 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="2" t="n"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>打开灯</t>
+          <t>停止闹钟</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -4680,7 +4680,7 @@
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -4688,22 +4688,22 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="2" t="n"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>关灯</t>
+          <t>开灯</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
@@ -4738,22 +4738,22 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="2" t="n"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>关闭灯</t>
+          <t>打开灯</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
@@ -4788,26 +4788,26 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="2" t="n"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>关灯</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0x001D</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -4845,19 +4845,19 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关闭灯</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>10001</v>
+        <v>30</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         </is>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -4888,26 +4888,26 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="2" t="n"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>防误</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>10002</v>
+        <v>31</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x001F</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4938,112 +4938,212 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="2" t="n"/>
       <c r="C90" t="inlineStr">
         <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>&lt;beep&gt;</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D92" s="2" t="n">
         <v>10003</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>0x00</t>
         </is>
       </c>
-      <c r="F90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="n">
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="91">
-      <c r="C91" t="inlineStr">
+    <row r="93">
+      <c r="C93" t="inlineStr">
         <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D93" t="n">
         <v>43605</v>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86 G87 H87 I87 J87 G88 H88 I88 J88" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5057,7 +5157,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -5272,7 +5372,7 @@
       <c r="B4" s="2" t="n"/>
       <c r="C4" t="inlineStr">
         <is>
-          <t>小沐小沐</t>
+          <t>你好灵犀</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -5322,7 +5422,7 @@
       <c r="B5" s="2" t="n"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hello小沐</t>
+          <t>灵犀你好</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
@@ -5334,7 +5434,7 @@
         </is>
       </c>
       <c r="F5" s="2" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
@@ -5372,7 +5472,7 @@
       <c r="B6" s="2" t="n"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>嗨小沐</t>
+          <t>小沐小沐</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
@@ -5384,7 +5484,7 @@
         </is>
       </c>
       <c r="F6" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
@@ -5422,7 +5522,7 @@
       <c r="B7" s="2" t="n"/>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hello摸摸</t>
+          <t>hello小沐</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
@@ -5472,7 +5572,7 @@
       <c r="B8" s="2" t="n"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hi摸摸</t>
+          <t>嗨小沐</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
@@ -5484,7 +5584,7 @@
         </is>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
@@ -5522,7 +5622,7 @@
       <c r="B9" s="2" t="n"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hello慕慕</t>
+          <t>hello摸摸</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
@@ -5572,7 +5672,7 @@
       <c r="B10" s="2" t="n"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hi慕慕</t>
+          <t>hi摸摸</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
@@ -5622,7 +5722,7 @@
       <c r="B11" s="2" t="n"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>AI模式</t>
+          <t>hello慕慕</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
@@ -5634,11 +5734,11 @@
         </is>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -5672,15 +5772,15 @@
       <c r="B12" s="2" t="n"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>聊天模式</t>
+          <t>hi慕慕</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0x000A</t>
+          <t>0x000B</t>
         </is>
       </c>
       <c r="F12" s="2" t="n">
@@ -5688,7 +5788,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -5715,22 +5815,22 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="2" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>翻译模式</t>
+          <t>AI模式</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0x000B</t>
+          <t>0x000C</t>
         </is>
       </c>
       <c r="F13" s="2" t="n">
@@ -5765,26 +5865,26 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="2" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>多语言模式</t>
+          <t>聊天模式</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0x000B</t>
+          <t>0x000C</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
@@ -5815,22 +5915,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>蓝牙模式</t>
+          <t>翻译模式</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000D</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -5865,14 +5965,14 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>放首歌</t>
+          <t>多语言模式</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
@@ -5884,7 +5984,7 @@
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -5922,19 +6022,19 @@
       <c r="B17" s="2" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>来首歌</t>
+          <t>蓝牙模式</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000E</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
@@ -5965,26 +6065,26 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>播放音乐</t>
+          <t>放首歌</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -6015,26 +6115,26 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="2" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>打开音乐</t>
+          <t>来首歌</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -6065,22 +6165,22 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>来点音乐</t>
+          <t>播放音乐</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
@@ -6115,22 +6215,22 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>来首音乐</t>
+          <t>打开音乐</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
@@ -6165,22 +6265,22 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>我要听歌</t>
+          <t>来点音乐</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -6215,22 +6315,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>我想听歌</t>
+          <t>来首音乐</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -6265,22 +6365,22 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>关闭音乐</t>
+          <t>我要听歌</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0x000E</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -6315,22 +6415,22 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>退出音乐</t>
+          <t>我想听歌</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0x000E</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -6365,26 +6465,26 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>静音</t>
+          <t>关闭音乐</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
@@ -6407,34 +6507,34 @@
         </is>
       </c>
       <c r="K26" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
         <v>16</v>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="n">
-        <v>15</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>闭嘴</t>
+          <t>退出音乐</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
@@ -6465,26 +6565,26 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>关音效</t>
+          <t>静音</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -6507,7 +6607,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -6515,26 +6615,26 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>关声音</t>
+          <t>闭嘴</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -6565,26 +6665,26 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>打开静音</t>
+          <t>关音效</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -6615,26 +6715,26 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="n"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>不要说话</t>
+          <t>关声音</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -6665,22 +6765,22 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="2" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>关闭音效</t>
+          <t>打开静音</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
@@ -6715,22 +6815,22 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="2" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>关闭声音</t>
+          <t>不要说话</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
@@ -6765,22 +6865,22 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="2" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>声音关闭</t>
+          <t>关闭音效</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -6815,26 +6915,26 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="2" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>把音效关了</t>
+          <t>关闭声音</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
@@ -6865,26 +6965,26 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="2" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>把声音关了</t>
+          <t>声音关闭</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
@@ -6915,26 +7015,26 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>开声音</t>
+          <t>把音效关了</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -6965,26 +7065,26 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="2" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>取消静音</t>
+          <t>把声音关了</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -7015,26 +7115,26 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="2" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>关闭静音</t>
+          <t>开声音</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -7065,22 +7165,22 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="2" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>打开声音</t>
+          <t>取消静音</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
@@ -7115,22 +7215,22 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="2" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>开启音量</t>
+          <t>关闭静音</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
@@ -7165,22 +7265,22 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="2" t="n"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>音效打开</t>
+          <t>打开声音</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -7215,22 +7315,22 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="2" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>声音打开</t>
+          <t>开启音量</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -7265,22 +7365,22 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="2" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>恢复声音</t>
+          <t>音效打开</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -7315,26 +7415,26 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="2" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>可以说话了</t>
+          <t>声音打开</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
@@ -7365,26 +7465,26 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="2" t="n"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>恢复声音</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
@@ -7415,14 +7515,14 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="2" t="n"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>播放</t>
+          <t>可以说话了</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
@@ -7434,7 +7534,7 @@
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -7457,7 +7557,7 @@
         </is>
       </c>
       <c r="K47" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -7472,19 +7572,19 @@
       <c r="B48" s="2" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>请播放</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -7515,26 +7615,26 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="2" t="n"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>继续播放</t>
+          <t>播放</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -7557,7 +7657,7 @@
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -7565,26 +7665,26 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="50">
       <c r="B50" s="2" t="n"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>取消暂停</t>
+          <t>请播放</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -7615,26 +7715,26 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="2" t="n"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>上一首</t>
+          <t>继续播放</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0x0013</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -7665,26 +7765,26 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="2" t="n"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>上一曲</t>
+          <t>取消暂停</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0x0013</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -7715,26 +7815,26 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="2" t="n"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>切歌</t>
+          <t>上一首</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0015</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -7765,22 +7865,22 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="2" t="n"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>下一首</t>
+          <t>上一曲</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0015</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
@@ -7815,26 +7915,26 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="2" t="n"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>下一曲</t>
+          <t>切歌</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -7865,22 +7965,22 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="2" t="n"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>换一首</t>
+          <t>下一首</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -7915,22 +8015,22 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="2" t="n"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>换一曲</t>
+          <t>下一曲</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
@@ -7965,26 +8065,26 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="2" t="n"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>音量最大</t>
+          <t>换一首</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
@@ -8015,26 +8115,26 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="2" t="n"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>声音最大</t>
+          <t>换一曲</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
@@ -8065,26 +8165,26 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="2" t="n"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>音量调到最大</t>
+          <t>音量最大</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -8115,22 +8215,22 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="2" t="n"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>音量最小</t>
+          <t>声音最大</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
@@ -8165,26 +8265,26 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="2" t="n"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>声音最小</t>
+          <t>音量调到最大</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -8215,26 +8315,26 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="2" t="n"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>音量调到最小</t>
+          <t>音量最小</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
@@ -8265,26 +8365,26 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="2" t="n"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>听不清</t>
+          <t>声音最小</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -8315,26 +8415,26 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="2" t="n"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>大声一点</t>
+          <t>音量调到最小</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -8365,26 +8465,26 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="2" t="n"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>音量调大</t>
+          <t>听不清</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -8407,7 +8507,7 @@
         </is>
       </c>
       <c r="K66" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -8415,26 +8515,26 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="2" t="n"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>声音大一点</t>
+          <t>大声一点</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -8465,26 +8565,26 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="2" t="n"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>声音太小了</t>
+          <t>音量调大</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -8507,7 +8607,7 @@
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -8515,26 +8615,26 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="2" t="n"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>把声音加大一点</t>
+          <t>声音大一点</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -8565,26 +8665,26 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="2" t="n"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>把音量加大一点</t>
+          <t>声音太小了</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -8615,26 +8715,26 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="2" t="n"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>小声一点</t>
+          <t>把声音加大一点</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -8665,26 +8765,26 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="2" t="n"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>音量调小</t>
+          <t>把音量加大一点</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -8715,26 +8815,26 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="2" t="n"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>声音小一点</t>
+          <t>小声一点</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -8765,26 +8865,26 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="2" t="n"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>声音太大了</t>
+          <t>音量调小</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -8815,26 +8915,26 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="2" t="n"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>把声音减小一点</t>
+          <t>声音小一点</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -8865,26 +8965,26 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="2" t="n"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>把音量减小一点</t>
+          <t>声音太大了</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -8915,26 +9015,26 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="2" t="n"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>设置闹钟</t>
+          <t>把声音减小一点</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -8965,26 +9065,26 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="2" t="n"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>设定闹钟</t>
+          <t>把音量减小一点</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -9015,22 +9115,22 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="2" t="n"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>打开闹钟</t>
+          <t>设置闹钟</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
@@ -9065,22 +9165,22 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="2" t="n"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>关闭闹钟</t>
+          <t>设定闹钟</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
@@ -9115,22 +9215,22 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="n"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>取消闹钟</t>
+          <t>打开闹钟</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -9165,22 +9265,22 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="2" t="n"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>停止闹钟</t>
+          <t>关闭闹钟</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -9215,26 +9315,26 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="2" t="n"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>开灯</t>
+          <t>取消闹钟</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
@@ -9257,7 +9357,7 @@
         </is>
       </c>
       <c r="K83" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -9265,26 +9365,26 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="2" t="n"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>打开灯</t>
+          <t>停止闹钟</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
@@ -9307,7 +9407,7 @@
         </is>
       </c>
       <c r="K84" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -9315,22 +9415,22 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="2" t="n"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>关灯</t>
+          <t>开灯</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
@@ -9365,22 +9465,22 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="2" t="n"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>关闭灯</t>
+          <t>打开灯</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
@@ -9415,26 +9515,26 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="2" t="n"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>关灯</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0x001D</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
@@ -9457,7 +9557,7 @@
         </is>
       </c>
       <c r="K87" s="2" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -9472,19 +9572,19 @@
       <c r="B88" s="2" t="n"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关闭灯</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>10001</v>
+        <v>30</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9607,7 @@
         </is>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -9515,26 +9615,26 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="2" t="n"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>防误</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>10002</v>
+        <v>31</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x001F</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -9557,7 +9657,7 @@
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -9565,112 +9665,212 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="90">
       <c r="B90" s="2" t="n"/>
       <c r="C90" t="inlineStr">
         <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="n">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="B91" s="2" t="n"/>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="B92" s="2" t="n"/>
+      <c r="C92" t="inlineStr">
+        <is>
           <t>&lt;beep&gt;</t>
         </is>
       </c>
-      <c r="D90" s="2" t="n">
+      <c r="D92" s="2" t="n">
         <v>10003</v>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>0x00</t>
         </is>
       </c>
-      <c r="F90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="n">
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="91">
-      <c r="C91" t="inlineStr">
+    <row r="93">
+      <c r="C93" t="inlineStr">
         <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D91" t="n">
+      <c r="D93" t="n">
         <v>43605</v>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K91" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86 G87 H87 I87 J87 G88 H88 I88 J88" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>

--- a/projects/offline_asr_llm_aiot_uart_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
+++ b/projects/offline_asr_llm_aiot_uart_sample/firmware/user_file/cmd_info/[60000]{cmd_info}.xlsx
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -1095,7 +1095,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI模式</t>
+          <t>小沐退下</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1145,15 +1145,15 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>聊天模式</t>
+          <t>灵犀退下</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000D</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1188,22 +1188,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>翻译模式</t>
+          <t>AI模式</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000E</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -1238,26 +1238,26 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>多语言模式</t>
+          <t>聊天模式</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000E</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -1288,22 +1288,22 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>蓝牙模式</t>
+          <t>翻译模式</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0x000E</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -1338,14 +1338,14 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>放首歌</t>
+          <t>多语言模式</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -1357,7 +1357,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -1395,19 +1395,19 @@
       <c r="B19" s="2" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>来首歌</t>
+          <t>蓝牙模式</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -1438,26 +1438,26 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>播放音乐</t>
+          <t>放首歌</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -1488,26 +1488,26 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>打开音乐</t>
+          <t>来首歌</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -1538,22 +1538,22 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>来点音乐</t>
+          <t>播放音乐</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -1588,22 +1588,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>来首音乐</t>
+          <t>打开音乐</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -1638,22 +1638,22 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>我要听歌</t>
+          <t>来点音乐</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -1688,22 +1688,22 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>我想听歌</t>
+          <t>来首音乐</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -1738,22 +1738,22 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>关闭音乐</t>
+          <t>我要听歌</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -1788,22 +1788,22 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>退出音乐</t>
+          <t>我想听歌</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -1838,26 +1838,26 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>静音</t>
+          <t>关闭音乐</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -1888,26 +1888,26 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>闭嘴</t>
+          <t>退出音乐</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -1938,26 +1938,26 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>关音效</t>
+          <t>静音</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -1980,7 +1980,7 @@
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -1988,26 +1988,26 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="n"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>关声音</t>
+          <t>闭嘴</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -2038,26 +2038,26 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="2" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>打开静音</t>
+          <t>关音效</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -2088,26 +2088,26 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="2" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>不要说话</t>
+          <t>关声音</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -2138,22 +2138,22 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="2" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>关闭音效</t>
+          <t>打开静音</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -2188,22 +2188,22 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="2" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>关闭声音</t>
+          <t>不要说话</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -2238,22 +2238,22 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="2" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>声音关闭</t>
+          <t>关闭音效</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -2288,26 +2288,26 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>把音效关了</t>
+          <t>关闭声音</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -2338,26 +2338,26 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="2" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>把声音关了</t>
+          <t>声音关闭</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -2388,26 +2388,26 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="2" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>开声音</t>
+          <t>把音效关了</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -2438,26 +2438,26 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="2" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>取消静音</t>
+          <t>把声音关了</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -2488,26 +2488,26 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="2" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>关闭静音</t>
+          <t>开声音</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -2538,22 +2538,22 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="2" t="n"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>打开声音</t>
+          <t>取消静音</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -2588,22 +2588,22 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="2" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>开启音量</t>
+          <t>关闭静音</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -2638,22 +2638,22 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="2" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>音效打开</t>
+          <t>打开声音</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -2688,22 +2688,22 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="2" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>声音打开</t>
+          <t>开启音量</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -2738,22 +2738,22 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="2" t="n"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>恢复声音</t>
+          <t>音效打开</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -2788,26 +2788,26 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="2" t="n"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>可以说话了</t>
+          <t>声音打开</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -2838,26 +2838,26 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="2" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>恢复声音</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0x0013</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -2888,14 +2888,14 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="2" t="n"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>播放</t>
+          <t>可以说话了</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2930,7 @@
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -2945,19 +2945,19 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>请播放</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0015</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -2988,26 +2988,26 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="2" t="n"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>继续播放</t>
+          <t>播放</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         </is>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -3038,26 +3038,26 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="2" t="n"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>取消暂停</t>
+          <t>请播放</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -3088,26 +3088,26 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="2" t="n"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>上一首</t>
+          <t>继续播放</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -3138,26 +3138,26 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="2" t="n"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>上一曲</t>
+          <t>取消暂停</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -3188,26 +3188,26 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="2" t="n"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>切歌</t>
+          <t>上一首</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -3238,22 +3238,22 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="2" t="n"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>下一首</t>
+          <t>上一曲</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -3288,26 +3288,26 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="2" t="n"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>下一曲</t>
+          <t>切歌</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -3338,22 +3338,22 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="2" t="n"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>换一首</t>
+          <t>下一首</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
@@ -3388,22 +3388,22 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="2" t="n"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>换一曲</t>
+          <t>下一曲</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
@@ -3438,26 +3438,26 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="2" t="n"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>音量最大</t>
+          <t>换一首</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -3488,26 +3488,26 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="2" t="n"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>声音最大</t>
+          <t>换一曲</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -3538,26 +3538,26 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="2" t="n"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>音量调到最大</t>
+          <t>音量最大</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -3588,22 +3588,22 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="2" t="n"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>音量最小</t>
+          <t>声音最大</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
@@ -3638,26 +3638,26 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="2" t="n"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>声音最小</t>
+          <t>音量调到最大</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -3688,26 +3688,26 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="2" t="n"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>音量调到最小</t>
+          <t>音量最小</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -3738,26 +3738,26 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="2" t="n"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>听不清</t>
+          <t>声音最小</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -3788,26 +3788,26 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="2" t="n"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>大声一点</t>
+          <t>音量调到最小</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -3838,26 +3838,26 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="2" t="n"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>音量调大</t>
+          <t>听不清</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -3888,26 +3888,26 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="2" t="n"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>声音大一点</t>
+          <t>大声一点</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -3938,26 +3938,26 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="2" t="n"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>声音太小了</t>
+          <t>音量调大</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -3980,7 +3980,7 @@
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -3988,26 +3988,26 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="2" t="n"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>把声音加大一点</t>
+          <t>声音大一点</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -4038,26 +4038,26 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="2" t="n"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>把音量加大一点</t>
+          <t>声音太小了</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -4088,26 +4088,26 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="2" t="n"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>小声一点</t>
+          <t>把声音加大一点</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -4138,26 +4138,26 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="2" t="n"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>音量调小</t>
+          <t>把音量加大一点</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -4188,26 +4188,26 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="2" t="n"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>声音小一点</t>
+          <t>小声一点</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -4238,26 +4238,26 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="2" t="n"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>声音太大了</t>
+          <t>音量调小</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -4288,26 +4288,26 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="2" t="n"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>把声音减小一点</t>
+          <t>声音小一点</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -4338,26 +4338,26 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="2" t="n"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>把音量减小一点</t>
+          <t>声音太大了</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -4388,26 +4388,26 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="2" t="n"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>设置闹钟</t>
+          <t>把声音减小一点</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -4438,26 +4438,26 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="2" t="n"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>设定闹钟</t>
+          <t>把音量减小一点</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -4488,22 +4488,22 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="n"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>打开闹钟</t>
+          <t>设置闹钟</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -4538,22 +4538,22 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="2" t="n"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>关闭闹钟</t>
+          <t>设定闹钟</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -4588,22 +4588,22 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="2" t="n"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>取消闹钟</t>
+          <t>打开闹钟</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
@@ -4638,22 +4638,22 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="2" t="n"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>停止闹钟</t>
+          <t>关闭闹钟</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
@@ -4688,26 +4688,26 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="2" t="n"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>开灯</t>
+          <t>取消闹钟</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0x001D</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -4730,7 +4730,7 @@
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -4738,26 +4738,26 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="2" t="n"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>打开灯</t>
+          <t>停止闹钟</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0x001D</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -4788,22 +4788,22 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="2" t="n"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>关灯</t>
+          <t>开灯</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0x001E</t>
+          <t>0x001F</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
@@ -4838,22 +4838,22 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="2" t="n"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>关闭灯</t>
+          <t>打开灯</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0x001E</t>
+          <t>0x001F</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -4888,26 +4888,26 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="2" t="n"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>关灯</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0x001F</t>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -4945,19 +4945,19 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关闭灯</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>10001</v>
+        <v>32</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -4980,7 +4980,7 @@
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -4988,26 +4988,26 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="2" t="n"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>防误</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>10002</v>
+        <v>33</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x0021</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -5030,7 +5030,7 @@
         </is>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -5038,112 +5038,212 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="2" t="n"/>
       <c r="C92" t="inlineStr">
         <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>&lt;beep&gt;</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D94" s="2" t="n">
         <v>10003</v>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>0x00</t>
         </is>
       </c>
-      <c r="F92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n">
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="93">
-      <c r="C93" t="inlineStr">
+    <row r="95">
+      <c r="C95" t="inlineStr">
         <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D95" t="n">
         <v>43605</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86 G87 H87 I87 J87 G88 H88 I88 J88" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86 G87 H87 I87 J87 G88 H88 I88 J88 G89 H89 I89 J89 G90 H90 I90 J90" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5157,7 +5257,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O93"/>
+  <dimension ref="A1:O95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col customWidth="1" max="1" min="1" width="18"/>
@@ -5822,7 +5922,7 @@
       <c r="B13" s="2" t="n"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AI模式</t>
+          <t>小沐退下</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -5838,7 +5938,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -5872,15 +5972,15 @@
       <c r="B14" s="2" t="n"/>
       <c r="C14" t="inlineStr">
         <is>
-          <t>聊天模式</t>
+          <t>灵犀退下</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0x000C</t>
+          <t>0x000D</t>
         </is>
       </c>
       <c r="F14" s="2" t="n">
@@ -5888,7 +5988,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -5915,22 +6015,22 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="2" t="n"/>
       <c r="C15" t="inlineStr">
         <is>
-          <t>翻译模式</t>
+          <t>AI模式</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000E</t>
         </is>
       </c>
       <c r="F15" s="2" t="n">
@@ -5965,26 +6065,26 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="2" t="n"/>
       <c r="C16" t="inlineStr">
         <is>
-          <t>多语言模式</t>
+          <t>聊天模式</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0x000D</t>
+          <t>0x000E</t>
         </is>
       </c>
       <c r="F16" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
@@ -6015,22 +6115,22 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="2" t="n"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>蓝牙模式</t>
+          <t>翻译模式</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0x000E</t>
+          <t>0x000F</t>
         </is>
       </c>
       <c r="F17" s="2" t="n">
@@ -6065,14 +6165,14 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="2" t="n"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>放首歌</t>
+          <t>多语言模式</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
@@ -6084,7 +6184,7 @@
         </is>
       </c>
       <c r="F18" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
@@ -6122,19 +6222,19 @@
       <c r="B19" s="2" t="n"/>
       <c r="C19" t="inlineStr">
         <is>
-          <t>来首歌</t>
+          <t>蓝牙模式</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0010</t>
         </is>
       </c>
       <c r="F19" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
@@ -6165,26 +6265,26 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="2" t="n"/>
       <c r="C20" t="inlineStr">
         <is>
-          <t>播放音乐</t>
+          <t>放首歌</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F20" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
@@ -6215,26 +6315,26 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="2" t="n"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>打开音乐</t>
+          <t>来首歌</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F21" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
@@ -6265,22 +6365,22 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="2" t="n"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>来点音乐</t>
+          <t>播放音乐</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F22" s="2" t="n">
@@ -6315,22 +6415,22 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" s="2" t="n"/>
       <c r="C23" t="inlineStr">
         <is>
-          <t>来首音乐</t>
+          <t>打开音乐</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F23" s="2" t="n">
@@ -6365,22 +6465,22 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" s="2" t="n"/>
       <c r="C24" t="inlineStr">
         <is>
-          <t>我要听歌</t>
+          <t>来点音乐</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F24" s="2" t="n">
@@ -6415,22 +6515,22 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25">
       <c r="B25" s="2" t="n"/>
       <c r="C25" t="inlineStr">
         <is>
-          <t>我想听歌</t>
+          <t>来首音乐</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0x000F</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F25" s="2" t="n">
@@ -6465,22 +6565,22 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="2" t="n"/>
       <c r="C26" t="inlineStr">
         <is>
-          <t>关闭音乐</t>
+          <t>我要听歌</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F26" s="2" t="n">
@@ -6515,22 +6615,22 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
       <c r="B27" s="2" t="n"/>
       <c r="C27" t="inlineStr">
         <is>
-          <t>退出音乐</t>
+          <t>我想听歌</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0x0010</t>
+          <t>0x0011</t>
         </is>
       </c>
       <c r="F27" s="2" t="n">
@@ -6565,26 +6665,26 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28">
       <c r="B28" s="2" t="n"/>
       <c r="C28" t="inlineStr">
         <is>
-          <t>静音</t>
+          <t>关闭音乐</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F28" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
@@ -6607,7 +6707,7 @@
         </is>
       </c>
       <c r="K28" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -6615,26 +6715,26 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29">
       <c r="B29" s="2" t="n"/>
       <c r="C29" t="inlineStr">
         <is>
-          <t>闭嘴</t>
+          <t>退出音乐</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0012</t>
         </is>
       </c>
       <c r="F29" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
@@ -6665,26 +6765,26 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" s="2" t="n"/>
       <c r="C30" t="inlineStr">
         <is>
-          <t>关音效</t>
+          <t>静音</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F30" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
@@ -6707,7 +6807,7 @@
         </is>
       </c>
       <c r="K30" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -6715,26 +6815,26 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" s="2" t="n"/>
       <c r="C31" t="inlineStr">
         <is>
-          <t>关声音</t>
+          <t>闭嘴</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F31" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
@@ -6765,26 +6865,26 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="B32" s="2" t="n"/>
       <c r="C32" t="inlineStr">
         <is>
-          <t>打开静音</t>
+          <t>关音效</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F32" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
@@ -6815,26 +6915,26 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" s="2" t="n"/>
       <c r="C33" t="inlineStr">
         <is>
-          <t>不要说话</t>
+          <t>关声音</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
@@ -6865,22 +6965,22 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="2" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
-          <t>关闭音效</t>
+          <t>打开静音</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F34" s="2" t="n">
@@ -6915,22 +7015,22 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" s="2" t="n"/>
       <c r="C35" t="inlineStr">
         <is>
-          <t>关闭声音</t>
+          <t>不要说话</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F35" s="2" t="n">
@@ -6965,22 +7065,22 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" s="2" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
-          <t>声音关闭</t>
+          <t>关闭音效</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F36" s="2" t="n">
@@ -7015,26 +7115,26 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" s="2" t="n"/>
       <c r="C37" t="inlineStr">
         <is>
-          <t>把音效关了</t>
+          <t>关闭声音</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F37" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
@@ -7065,26 +7165,26 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" s="2" t="n"/>
       <c r="C38" t="inlineStr">
         <is>
-          <t>把声音关了</t>
+          <t>声音关闭</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0x0011</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F38" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
@@ -7115,26 +7215,26 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" s="2" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
-          <t>开声音</t>
+          <t>把音效关了</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F39" s="2" t="n">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
@@ -7165,26 +7265,26 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="40">
       <c r="B40" s="2" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
-          <t>取消静音</t>
+          <t>把声音关了</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0013</t>
         </is>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
@@ -7215,26 +7315,26 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" s="2" t="n"/>
       <c r="C41" t="inlineStr">
         <is>
-          <t>关闭静音</t>
+          <t>开声音</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
@@ -7265,22 +7365,22 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
       <c r="B42" s="2" t="n"/>
       <c r="C42" t="inlineStr">
         <is>
-          <t>打开声音</t>
+          <t>取消静音</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F42" s="2" t="n">
@@ -7315,22 +7415,22 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" s="2" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
-          <t>开启音量</t>
+          <t>关闭静音</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F43" s="2" t="n">
@@ -7365,22 +7465,22 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="2" t="n"/>
       <c r="C44" t="inlineStr">
         <is>
-          <t>音效打开</t>
+          <t>打开声音</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F44" s="2" t="n">
@@ -7415,22 +7515,22 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" s="2" t="n"/>
       <c r="C45" t="inlineStr">
         <is>
-          <t>声音打开</t>
+          <t>开启音量</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F45" s="2" t="n">
@@ -7465,22 +7565,22 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="46">
       <c r="B46" s="2" t="n"/>
       <c r="C46" t="inlineStr">
         <is>
-          <t>恢复声音</t>
+          <t>音效打开</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F46" s="2" t="n">
@@ -7515,26 +7615,26 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="47">
       <c r="B47" s="2" t="n"/>
       <c r="C47" t="inlineStr">
         <is>
-          <t>可以说话了</t>
+          <t>声音打开</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0x0012</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F47" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
@@ -7565,26 +7665,26 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="B48" s="2" t="n"/>
       <c r="C48" t="inlineStr">
         <is>
-          <t>暂停</t>
+          <t>恢复声音</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0x0013</t>
+          <t>0x0014</t>
         </is>
       </c>
       <c r="F48" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
@@ -7615,14 +7715,14 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="49">
       <c r="B49" s="2" t="n"/>
       <c r="C49" t="inlineStr">
         <is>
-          <t>播放</t>
+          <t>可以说话了</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
@@ -7634,7 +7734,7 @@
         </is>
       </c>
       <c r="F49" s="2" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
@@ -7657,7 +7757,7 @@
         </is>
       </c>
       <c r="K49" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -7672,19 +7772,19 @@
       <c r="B50" s="2" t="n"/>
       <c r="C50" t="inlineStr">
         <is>
-          <t>请播放</t>
+          <t>暂停</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0015</t>
         </is>
       </c>
       <c r="F50" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
@@ -7715,26 +7815,26 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="51">
       <c r="B51" s="2" t="n"/>
       <c r="C51" t="inlineStr">
         <is>
-          <t>继续播放</t>
+          <t>播放</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F51" s="2" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
@@ -7757,7 +7857,7 @@
         </is>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -7765,26 +7865,26 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="B52" s="2" t="n"/>
       <c r="C52" t="inlineStr">
         <is>
-          <t>取消暂停</t>
+          <t>请播放</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0x0014</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F52" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
@@ -7815,26 +7915,26 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="53">
       <c r="B53" s="2" t="n"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>上一首</t>
+          <t>继续播放</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F53" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
@@ -7865,26 +7965,26 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="54">
       <c r="B54" s="2" t="n"/>
       <c r="C54" t="inlineStr">
         <is>
-          <t>上一曲</t>
+          <t>取消暂停</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>0x0015</t>
+          <t>0x0016</t>
         </is>
       </c>
       <c r="F54" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
@@ -7915,26 +8015,26 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="55">
       <c r="B55" s="2" t="n"/>
       <c r="C55" t="inlineStr">
         <is>
-          <t>切歌</t>
+          <t>上一首</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F55" s="2" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
@@ -7965,22 +8065,22 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="B56" s="2" t="n"/>
       <c r="C56" t="inlineStr">
         <is>
-          <t>下一首</t>
+          <t>上一曲</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0017</t>
         </is>
       </c>
       <c r="F56" s="2" t="n">
@@ -8015,26 +8115,26 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57">
       <c r="B57" s="2" t="n"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>下一曲</t>
+          <t>切歌</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F57" s="2" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
@@ -8065,22 +8165,22 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="58">
       <c r="B58" s="2" t="n"/>
       <c r="C58" t="inlineStr">
         <is>
-          <t>换一首</t>
+          <t>下一首</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F58" s="2" t="n">
@@ -8115,22 +8215,22 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="59">
       <c r="B59" s="2" t="n"/>
       <c r="C59" t="inlineStr">
         <is>
-          <t>换一曲</t>
+          <t>下一曲</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>0x0016</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F59" s="2" t="n">
@@ -8165,26 +8265,26 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="60">
       <c r="B60" s="2" t="n"/>
       <c r="C60" t="inlineStr">
         <is>
-          <t>音量最大</t>
+          <t>换一首</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F60" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
@@ -8215,26 +8315,26 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="B61" s="2" t="n"/>
       <c r="C61" t="inlineStr">
         <is>
-          <t>声音最大</t>
+          <t>换一曲</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0018</t>
         </is>
       </c>
       <c r="F61" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
@@ -8265,26 +8365,26 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="62">
       <c r="B62" s="2" t="n"/>
       <c r="C62" t="inlineStr">
         <is>
-          <t>音量调到最大</t>
+          <t>音量最大</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>0x0017</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F62" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
@@ -8315,22 +8415,22 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="63">
       <c r="B63" s="2" t="n"/>
       <c r="C63" t="inlineStr">
         <is>
-          <t>音量最小</t>
+          <t>声音最大</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F63" s="2" t="n">
@@ -8365,26 +8465,26 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="64">
       <c r="B64" s="2" t="n"/>
       <c r="C64" t="inlineStr">
         <is>
-          <t>声音最小</t>
+          <t>音量调到最大</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x0019</t>
         </is>
       </c>
       <c r="F64" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
@@ -8415,26 +8515,26 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="2" t="n"/>
       <c r="C65" t="inlineStr">
         <is>
-          <t>音量调到最小</t>
+          <t>音量最小</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>0x0018</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F65" s="2" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -8465,26 +8565,26 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="2" t="n"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>听不清</t>
+          <t>声音最小</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F66" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
@@ -8515,26 +8615,26 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
       <c r="B67" s="2" t="n"/>
       <c r="C67" t="inlineStr">
         <is>
-          <t>大声一点</t>
+          <t>音量调到最小</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001A</t>
         </is>
       </c>
       <c r="F67" s="2" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
@@ -8565,26 +8665,26 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="68">
       <c r="B68" s="2" t="n"/>
       <c r="C68" t="inlineStr">
         <is>
-          <t>音量调大</t>
+          <t>听不清</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F68" s="2" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
@@ -8607,7 +8707,7 @@
         </is>
       </c>
       <c r="K68" s="2" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -8615,26 +8715,26 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
       <c r="B69" s="2" t="n"/>
       <c r="C69" t="inlineStr">
         <is>
-          <t>声音大一点</t>
+          <t>大声一点</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F69" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
@@ -8665,26 +8765,26 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="B70" s="2" t="n"/>
       <c r="C70" t="inlineStr">
         <is>
-          <t>声音太小了</t>
+          <t>音量调大</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F70" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
@@ -8707,7 +8807,7 @@
         </is>
       </c>
       <c r="K70" s="2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -8715,26 +8815,26 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="2" t="n"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>把声音加大一点</t>
+          <t>声音大一点</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F71" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
@@ -8765,26 +8865,26 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="B72" s="2" t="n"/>
       <c r="C72" t="inlineStr">
         <is>
-          <t>把音量加大一点</t>
+          <t>声音太小了</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>0x0019</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F72" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
@@ -8815,26 +8915,26 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
       <c r="B73" s="2" t="n"/>
       <c r="C73" t="inlineStr">
         <is>
-          <t>小声一点</t>
+          <t>把声音加大一点</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F73" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
@@ -8865,26 +8965,26 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74">
       <c r="B74" s="2" t="n"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>音量调小</t>
+          <t>把音量加大一点</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001B</t>
         </is>
       </c>
       <c r="F74" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
@@ -8915,26 +9015,26 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
       <c r="B75" s="2" t="n"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>声音小一点</t>
+          <t>小声一点</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F75" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
@@ -8965,26 +9065,26 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="2" t="n"/>
       <c r="C76" t="inlineStr">
         <is>
-          <t>声音太大了</t>
+          <t>音量调小</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F76" s="2" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
@@ -9015,26 +9115,26 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="77">
       <c r="B77" s="2" t="n"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>把声音减小一点</t>
+          <t>声音小一点</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F77" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
@@ -9065,26 +9165,26 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="78">
       <c r="B78" s="2" t="n"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>把音量减小一点</t>
+          <t>声音太大了</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>0x001A</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F78" s="2" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
@@ -9115,26 +9215,26 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="79">
       <c r="B79" s="2" t="n"/>
       <c r="C79" t="inlineStr">
         <is>
-          <t>设置闹钟</t>
+          <t>把声音减小一点</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F79" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
@@ -9165,26 +9265,26 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="80">
       <c r="B80" s="2" t="n"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>设定闹钟</t>
+          <t>把音量减小一点</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001C</t>
         </is>
       </c>
       <c r="F80" s="2" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
@@ -9215,22 +9315,22 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="81">
       <c r="B81" s="2" t="n"/>
       <c r="C81" t="inlineStr">
         <is>
-          <t>打开闹钟</t>
+          <t>设置闹钟</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>0x001B</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F81" s="2" t="n">
@@ -9265,22 +9365,22 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="82">
       <c r="B82" s="2" t="n"/>
       <c r="C82" t="inlineStr">
         <is>
-          <t>关闭闹钟</t>
+          <t>设定闹钟</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F82" s="2" t="n">
@@ -9315,22 +9415,22 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="83">
       <c r="B83" s="2" t="n"/>
       <c r="C83" t="inlineStr">
         <is>
-          <t>取消闹钟</t>
+          <t>打开闹钟</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001D</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
@@ -9365,22 +9465,22 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="84">
       <c r="B84" s="2" t="n"/>
       <c r="C84" t="inlineStr">
         <is>
-          <t>停止闹钟</t>
+          <t>关闭闹钟</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0x001C</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
@@ -9415,26 +9515,26 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="85">
       <c r="B85" s="2" t="n"/>
       <c r="C85" t="inlineStr">
         <is>
-          <t>开灯</t>
+          <t>取消闹钟</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>0x001D</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F85" s="2" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
@@ -9457,7 +9557,7 @@
         </is>
       </c>
       <c r="K85" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -9465,26 +9565,26 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="86">
       <c r="B86" s="2" t="n"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>打开灯</t>
+          <t>停止闹钟</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>0x001D</t>
+          <t>0x001E</t>
         </is>
       </c>
       <c r="F86" s="2" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
@@ -9507,7 +9607,7 @@
         </is>
       </c>
       <c r="K86" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -9515,22 +9615,22 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="87">
       <c r="B87" s="2" t="n"/>
       <c r="C87" t="inlineStr">
         <is>
-          <t>关灯</t>
+          <t>开灯</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>0x001E</t>
+          <t>0x001F</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
@@ -9565,22 +9665,22 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="88">
       <c r="B88" s="2" t="n"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>关闭灯</t>
+          <t>打开灯</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>0x001E</t>
+          <t>0x001F</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
@@ -9615,26 +9715,26 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="89">
       <c r="B89" s="2" t="n"/>
       <c r="C89" t="inlineStr">
         <is>
-          <t>防误</t>
+          <t>关灯</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>0x001F</t>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
-        <v>200</v>
+        <v>60</v>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
@@ -9657,7 +9757,7 @@
         </is>
       </c>
       <c r="K89" s="2" t="n">
-        <v>90</v>
+        <v>12</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -9672,19 +9772,19 @@
       <c r="B90" s="2" t="n"/>
       <c r="C90" t="inlineStr">
         <is>
-          <t>&lt;welcome&gt;</t>
+          <t>关闭灯</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>10001</v>
+        <v>32</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x0020</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
@@ -9707,7 +9807,7 @@
         </is>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -9715,26 +9815,26 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="91">
       <c r="B91" s="2" t="n"/>
       <c r="C91" t="inlineStr">
         <is>
-          <t>&lt;inactivate&gt;</t>
+          <t>防误</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>10002</v>
+        <v>33</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>0x00</t>
+          <t>0x0021</t>
         </is>
       </c>
       <c r="F91" s="2" t="n">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
@@ -9757,7 +9857,7 @@
         </is>
       </c>
       <c r="K91" s="2" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -9765,112 +9865,212 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
     </row>
     <row r="92">
       <c r="B92" s="2" t="n"/>
       <c r="C92" t="inlineStr">
         <is>
+          <t>&lt;welcome&gt;</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>10001</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="n">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="B93" s="2" t="n"/>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>&lt;inactivate&gt;</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>10002</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>0x00</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="B94" s="2" t="n"/>
+      <c r="C94" t="inlineStr">
+        <is>
           <t>&lt;beep&gt;</t>
         </is>
       </c>
-      <c r="D92" s="2" t="n">
+      <c r="D94" s="2" t="n">
         <v>10003</v>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E94" t="inlineStr">
         <is>
           <t>0x00</t>
         </is>
       </c>
-      <c r="F92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="n">
+      <c r="F94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="n">
         <v>1000</v>
       </c>
     </row>
-    <row r="93">
-      <c r="C93" t="inlineStr">
+    <row r="95">
+      <c r="C95" t="inlineStr">
         <is>
           <t>&lt;baud_sync_req&gt;</t>
         </is>
       </c>
-      <c r="D93" t="n">
+      <c r="D95" t="n">
         <v>43605</v>
       </c>
-      <c r="E93" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>0xAA55</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>0</v>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="K93" t="n">
-        <v>0</v>
-      </c>
-      <c r="L93" t="inlineStr">
-        <is>
-          <t>user_defined</t>
-        </is>
-      </c>
-      <c r="M93" t="inlineStr"/>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>0</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>user_defined</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86 G87 H87 I87 J87 G88 H88 I88 J88" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="G2 H2 I2 J2 G3 H3 I3 J3 G4 H4 I4 J4 G5 H5 I5 J5 G6 H6 I6 J6 G7 H7 I7 J7 G8 H8 I8 J8 G9 H9 I9 J9 G10 H10 I10 J10 G11 H11 I11 J11 G12 H12 I12 J12 G13 H13 I13 J13 G14 H14 I14 J14 G15 H15 I15 J15 G16 H16 I16 J16 G17 H17 I17 J17 G18 H18 I18 J18 G19 H19 I19 J19 G20 H20 I20 J20 G21 H21 I21 J21 G22 H22 I22 J22 G23 H23 I23 J23 G24 H24 I24 J24 G25 H25 I25 J25 G26 H26 I26 J26 G27 H27 I27 J27 G28 H28 I28 J28 G29 H29 I29 J29 G30 H30 I30 J30 G31 H31 I31 J31 G32 H32 I32 J32 G33 H33 I33 J33 G34 H34 I34 J34 G35 H35 I35 J35 G36 H36 I36 J36 G37 H37 I37 J37 G38 H38 I38 J38 G39 H39 I39 J39 G40 H40 I40 J40 G41 H41 I41 J41 G42 H42 I42 J42 G43 H43 I43 J43 G44 H44 I44 J44 G45 H45 I45 J45 G46 H46 I46 J46 G47 H47 I47 J47 G48 H48 I48 J48 G49 H49 I49 J49 G50 H50 I50 J50 G51 H51 I51 J51 G52 H52 I52 J52 G53 H53 I53 J53 G54 H54 I54 J54 G55 H55 I55 J55 G56 H56 I56 J56 G57 H57 I57 J57 G58 H58 I58 J58 G59 H59 I59 J59 G60 H60 I60 J60 G61 H61 I61 J61 G62 H62 I62 J62 G63 H63 I63 J63 G64 H64 I64 J64 G65 H65 I65 J65 G66 H66 I66 J66 G67 H67 I67 J67 G68 H68 I68 J68 G69 H69 I69 J69 G70 H70 I70 J70 G71 H71 I71 J71 G72 H72 I72 J72 G73 H73 I73 J73 G74 H74 I74 J74 G75 H75 I75 J75 G76 H76 I76 J76 G77 H77 I77 J77 G78 H78 I78 J78 G79 H79 I79 J79 G80 H80 I80 J80 G81 H81 I81 J81 G82 H82 I82 J82 G83 H83 I83 J83 G84 H84 I84 J84 G85 H85 I85 J85 G86 H86 I86 J86 G87 H87 I87 J87 G88 H88 I88 J88 G89 H89 I89 J89 G90 H90 I90 J90" type="list">
       <formula1>"YES,NO"</formula1>
     </dataValidation>
-    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88" type="list">
+    <dataValidation allowBlank="1" error="Your entry is not in the list" errorTitle="Invalid Entry" prompt="Please select from the list" promptTitle="List Selection" showErrorMessage="1" showInputMessage="1" sqref="L2 L3 L4 L5 L6 L7 L8 L9 L10 L11 L12 L13 L14 L15 L16 L17 L18 L19 L20 L21 L22 L23 L24 L25 L26 L27 L28 L29 L30 L31 L32 L33 L34 L35 L36 L37 L38 L39 L40 L41 L42 L43 L44 L45 L46 L47 L48 L49 L50 L51 L52 L53 L54 L55 L56 L57 L58 L59 L60 L61 L62 L63 L64 L65 L66 L67 L68 L69 L70 L71 L72 L73 L74 L75 L76 L77 L78 L79 L80 L81 L82 L83 L84 L85 L86 L87 L88 L89 L90" type="list">
       <formula1>"user_defined,random"</formula1>
     </dataValidation>
   </dataValidations>
